--- a/output/pdf_financials_xlsx/PHD.xlsx
+++ b/output/pdf_financials_xlsx/PHD.xlsx
@@ -889,40 +889,40 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.001822</v>
+        <v>0.103064</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.038446</v>
+        <v>0.383451</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.037083</v>
+        <v>0.187379</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.08275100000000001</v>
+        <v>0.349986</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.048643</v>
+        <v>0.266647</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.027293</v>
+        <v>0.195552</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.092539</v>
+        <v>0.655268</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.030348</v>
+        <v>0.351834</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.197003</v>
+        <v>0.72478</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.183924</v>
+        <v>0.741206</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.267153</v>
+        <v>0.644602</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.064793</v>
+        <v>0.332155</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>0.31278</v>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.001822</v>
+        <v>-0.103064</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -974,19 +974,19 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.030348</v>
+        <v>-0.351834</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.197003</v>
+        <v>-0.72478</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.183924</v>
+        <v>-0.741206</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.267153</v>
+        <v>-0.644602</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.064793</v>
+        <v>-0.332155</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-0.31278</v>
@@ -1026,7 +1026,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000197</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>-0.649742</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.326637</v>
+        <v>-0.326834</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.718322</v>
@@ -1980,7 +1980,7 @@
         <v>-0.649742</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.326637</v>
+        <v>-0.326834</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.718322</v>
@@ -2237,46 +2237,46 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.619281</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.093831</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.031115</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.042141</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.02046</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.313011</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.511692</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.027829</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.514455</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.053197</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004816</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.002634</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.003499</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.010356</v>
       </c>
     </row>
     <row r="35">
@@ -2341,46 +2341,46 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.619281</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.093831</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.031115</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.042141</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.02046</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.313011</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.511692</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.027829</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.514455</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.053197</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004816</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.002634</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.003499</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.010356</v>
       </c>
     </row>
     <row r="37">
@@ -2965,46 +2965,46 @@
         <v>0.146148</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.619281</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.445488</v>
+        <v>0.351657</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.162069</v>
+        <v>1.130954</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.042141</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.02046</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.330804</v>
+        <v>0.017793</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.78966</v>
+        <v>0.277968</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.088197</v>
+        <v>0.060368</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.568742</v>
+        <v>0.054287</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.080734</v>
+        <v>0.027537</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.012182</v>
+        <v>0.007366</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.002634</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.060332</v>
+        <v>0.056833</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.017975</v>
+        <v>0.007619</v>
       </c>
     </row>
     <row r="49">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -26302,47 +26302,47 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E211" s="5" t="n">
-        <v>-0.103064</v>
+        <v>0.103064</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>-0.383451</v>
+        <v>0.383451</v>
       </c>
       <c r="G211" s="5" t="n">
-        <v>-0.187379</v>
+        <v>0.187379</v>
       </c>
       <c r="H211" s="5" t="n">
-        <v>-0.349986</v>
+        <v>0.349986</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>-0.266647</v>
+        <v>0.266647</v>
       </c>
       <c r="J211" s="5" t="n">
-        <v>-0.195552</v>
+        <v>0.195552</v>
       </c>
       <c r="K211" s="5" t="n">
-        <v>-0.655268</v>
+        <v>0.655268</v>
       </c>
       <c r="L211" s="5" t="n">
-        <v>-0.351834</v>
+        <v>0.351834</v>
       </c>
       <c r="M211" s="5" t="n">
-        <v>-0.72478</v>
+        <v>0.72478</v>
       </c>
       <c r="N211" s="5" t="n">
-        <v>-0.741206</v>
+        <v>0.741206</v>
       </c>
       <c r="O211" s="5" t="n">
-        <v>-0.644602</v>
+        <v>0.644602</v>
       </c>
       <c r="P211" s="5" t="n">
-        <v>-0.332155</v>
+        <v>0.332155</v>
       </c>
       <c r="Q211" s="5" t="n">
-        <v>-0.31278</v>
+        <v>0.31278</v>
       </c>
       <c r="R211" t="inlineStr">
         <is>
@@ -28404,7 +28404,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">

--- a/output/pdf_financials_xlsx/PHD.xlsx
+++ b/output/pdf_financials_xlsx/PHD.xlsx
@@ -733,49 +733,49 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.001822</v>
+        <v>0.008151</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.038446</v>
+        <v>0.111278</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.037083</v>
+        <v>0.109263</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.08275100000000001</v>
+        <v>0.145636</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.048643</v>
+        <v>0.112852</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.027293</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.092539</v>
+        <v>0.378858</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.030348</v>
+        <v>0.095855</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.197003</v>
+        <v>0.254555</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.168924</v>
+        <v>0.325424</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.190153</v>
+        <v>0.356101</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.059793</v>
+        <v>0.216539</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.047872</v>
+        <v>0.198912</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.016496</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.03048</v>
+        <v>0.11448</v>
       </c>
     </row>
     <row r="8">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.138148</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.619281</v>
@@ -2292,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>0.351657</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0</v>
+        <v>1.130954</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -2338,16 +2338,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.138148</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.619281</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.093831</v>
+        <v>0.445488</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.031115</v>
+        <v>1.162069</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.042141</v>
@@ -2962,16 +2962,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.146148</v>
+        <v>0.008</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.351657</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.130954</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3539,7 +3539,7 @@
         <v>2.028347</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>2.323383</v>
+        <v>2.360091</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>2.591851</v>
@@ -3695,7 +3695,7 @@
         <v>0.007678</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.042428</v>
+        <v>0.00572</v>
       </c>
       <c r="L61" s="3" t="n">
         <v>0.003879</v>
@@ -5142,49 +5142,49 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>0.283</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>0.9736629999999999</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>0.970846</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>1.092346</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>1.092346</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>1.277317</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>2.52995</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>3.645023</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>4.442522</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>5.834604</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>6.16971</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>6.19446</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>6.254762</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>6.254762</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>6.376702</v>
       </c>
     </row>
     <row r="89">
@@ -8455,7 +8455,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -9185,7 +9189,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -9877,7 +9885,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -10608,7 +10620,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -10770,7 +10786,11 @@
           <t>Right-of-use asset – Note 6</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12372,7 +12392,11 @@
           <t>Short-term investment - Note 5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13284,7 +13308,11 @@
           <t>Cash – Note 5 $</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.138148</v>
       </c>
@@ -14026,7 +14054,11 @@
           <t>Share capital – Notes 6, 7</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>0.283</v>
       </c>
@@ -21035,7 +21067,11 @@
           <t>Share-based payments – Note 6</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -24653,7 +24689,11 @@
           <t>Management fees – Note 7</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -25774,7 +25814,11 @@
           <t>Consulting fees – Note 7</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -25940,7 +25984,11 @@
           <t>Rent – Note 7</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -26893,7 +26941,11 @@
           <t>Consulting fees – Note 8</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -27067,7 +27119,11 @@
           <t>Management fees – Note 8</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -27514,7 +27570,11 @@
           <t>Amortization – Note 6</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -28141,7 +28201,11 @@
           <t>Office, rent and administration – Note 7</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -31280,7 +31344,11 @@
           <t>Office, rent and administration – Note 9</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>0.006329</v>
       </c>
@@ -31998,7 +32066,11 @@
           <t>Weighted average shares outstanding – Note 11</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PHD.xlsx
+++ b/output/pdf_financials_xlsx/PHD.xlsx
@@ -754,7 +754,7 @@
         <v>0.378858</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.095855</v>
+        <v>0.121745</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.254555</v>
@@ -15211,7 +15211,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -16291,7 +16295,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -16892,7 +16900,11 @@
           <t>Allocated from share capital to equity reserves relating to unit warrants from a private placement $</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -18935,7 +18947,11 @@
           <t>Allocated from share capital to equity reserves relating to unit warrants from a private placement $</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -21621,7 +21637,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -27752,7 +27772,11 @@
           <t>Director’s fees – Note 7</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -30272,7 +30296,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -30634,7 +30662,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -31607,7 +31639,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -32248,7 +32284,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -32883,7 +32923,11 @@
           <t>Interest revenue</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
